--- a/artfynd/A 22427-2025 artfynd.xlsx
+++ b/artfynd/A 22427-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>126679721</v>
       </c>
       <c r="B4" t="n">
-        <v>98397</v>
+        <v>98472</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22427-2025 artfynd.xlsx
+++ b/artfynd/A 22427-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>126679721</v>
       </c>
       <c r="B4" t="n">
-        <v>98472</v>
+        <v>98478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22427-2025 artfynd.xlsx
+++ b/artfynd/A 22427-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>126679721</v>
       </c>
       <c r="B4" t="n">
-        <v>98478</v>
+        <v>98479</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22427-2025 artfynd.xlsx
+++ b/artfynd/A 22427-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>126679223</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22427-2025 artfynd.xlsx
+++ b/artfynd/A 22427-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>126679223</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22427-2025 artfynd.xlsx
+++ b/artfynd/A 22427-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>126679223</v>
       </c>
       <c r="B3" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22427-2025 artfynd.xlsx
+++ b/artfynd/A 22427-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>126679721</v>
       </c>
       <c r="B4" t="n">
-        <v>98479</v>
+        <v>98472</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22427-2025 artfynd.xlsx
+++ b/artfynd/A 22427-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>126679721</v>
       </c>
       <c r="B4" t="n">
-        <v>98472</v>
+        <v>98479</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22427-2025 artfynd.xlsx
+++ b/artfynd/A 22427-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117614612</v>
+        <v>117140632</v>
       </c>
       <c r="B2" t="n">
-        <v>79563</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Blomsteråsen, Mpd</t>
+          <t>Honkasosvedjan, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>606321</v>
+        <v>606465</v>
       </c>
       <c r="R2" t="n">
-        <v>6958756</v>
+        <v>6958781</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126679223</v>
+        <v>117614612</v>
       </c>
       <c r="B3" t="n">
-        <v>57741</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,39 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Killinghalsmyran, Mpd</t>
+          <t>Blomsteråsen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>606439</v>
+        <v>606321</v>
       </c>
       <c r="R3" t="n">
-        <v>6958766</v>
+        <v>6958756</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,17 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,49 +861,50 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126679721</v>
+        <v>126679177</v>
       </c>
       <c r="B4" t="n">
-        <v>98479</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223621</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>11</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -923,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>606395</v>
+        <v>606438</v>
       </c>
       <c r="R4" t="n">
-        <v>6958787</v>
+        <v>6958811</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,6 +951,11 @@
           <t>2025-07-15</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -982,6 +977,214 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126679223</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Killinghalsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>606439</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6958766</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126679721</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99155</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Killinghalsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>606395</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6958787</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22427-2025 artfynd.xlsx
+++ b/artfynd/A 22427-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140632</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117614612</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126679177</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126679223</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,8 +1210,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126679721</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>